--- a/outputs/llp_planner_results.xlsx
+++ b/outputs/llp_planner_results.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\outputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817F9C71-502E-468B-BFBF-77424955013C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32460" yWindow="1170" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Trade_Flows" sheetId="1" r:id="rId1"/>
     <sheet name="Regional_Summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="23">
   <si>
     <t>exp</t>
   </si>
@@ -56,6 +50,18 @@
     <t>2025</t>
   </si>
   <si>
+    <t>2030</t>
+  </si>
+  <si>
+    <t>2035</t>
+  </si>
+  <si>
+    <t>2040</t>
+  </si>
+  <si>
+    <t>2045</t>
+  </si>
+  <si>
     <t>region</t>
   </si>
   <si>
@@ -68,7 +74,7 @@
     <t>lam</t>
   </si>
   <si>
-    <t>mu</t>
+    <t>mu_cap</t>
   </si>
   <si>
     <t>Dmax</t>
@@ -78,23 +84,22 @@
   </si>
   <si>
     <t>c_man</t>
-  </si>
-  <si>
-    <t>2030</t>
-  </si>
-  <si>
-    <t>2035</t>
-  </si>
-  <si>
-    <t>2040</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -110,7 +115,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -118,33 +123,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -182,7 +197,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -216,7 +231,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -251,10 +265,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -427,25 +440,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -459,74 +472,536 @@
         <v>278</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>599.9999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>58.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>38.270000000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>49.08</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7">
+        <v>58.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>216.3600000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>38.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>3.120000000000042</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>49.08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19">
+        <v>238.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>301.2800000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21">
+        <v>285.0399999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <v>83.59999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <v>82.60000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27">
         <v>27.61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>90.56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33">
+        <v>33.63999999999972</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34">
+        <v>111.88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35">
+        <v>136.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36">
+        <v>158.72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37">
+        <v>174.96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40">
+        <v>7.399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -535,51 +1010,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.54296875" customWidth="1"/>
-    <col min="6" max="6" width="13.90625" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="24.26953125" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -596,682 +1060,856 @@
         <v>163</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2">
         <v>278</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>931</v>
       </c>
       <c r="I2">
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>961.5599999999999</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3">
         <v>410</v>
       </c>
       <c r="H3">
-        <v>20</v>
+        <v>931</v>
       </c>
       <c r="I3">
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1205</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>251.9695784211183</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>88.96957842111833</v>
       </c>
       <c r="G4">
         <v>540</v>
       </c>
       <c r="H4">
-        <v>20</v>
+        <v>931</v>
       </c>
       <c r="I4">
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1342</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>310.117</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>147.117</v>
       </c>
       <c r="G5">
         <v>600</v>
       </c>
       <c r="H5">
-        <v>20</v>
+        <v>931</v>
       </c>
       <c r="I5">
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>58.99</v>
+        <v>600</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1479</v>
       </c>
       <c r="E6">
-        <v>179.11799999999999</v>
+        <v>283.132</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>120.132</v>
       </c>
       <c r="G6">
-        <v>58.99</v>
+        <v>600</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>931</v>
       </c>
       <c r="I6">
-        <v>299.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>58.99</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>179.118</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G7">
-        <v>68</v>
+        <v>58.99</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7">
         <v>299.25</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>179.118</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G8">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I8">
         <v>299.25</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>268.0875784211183</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G9">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I9">
         <v>299.25</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>38.270000000000003</v>
+        <v>250</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E10">
-        <v>174.13300000000001</v>
+        <v>326.235</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>26.98499999999995</v>
       </c>
       <c r="G10">
-        <v>38.270000000000003</v>
+        <v>250</v>
       </c>
       <c r="H10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I10">
-        <v>321.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>33.63999999999972</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>299.25</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G11">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I11">
-        <v>321.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>38.27</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>174.133</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G12">
-        <v>95</v>
+        <v>38.27</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I12">
         <v>321.25</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>174.133</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="H13">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I13">
         <v>321.25</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>49.08</v>
+        <v>95</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>176.78042157888169</v>
+        <v>263.1025784211183</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G14">
-        <v>49.08</v>
+        <v>95</v>
       </c>
       <c r="H14">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>265.75204563977178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>111.88</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>321.25</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G15">
-        <v>290</v>
+        <v>115</v>
       </c>
       <c r="H15">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>265.75204563977178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>294.265</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G16">
-        <v>375</v>
+        <v>115</v>
       </c>
       <c r="H16">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I16">
-        <v>265.75204563977178</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>49.08</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>176.7804215788817</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G17">
-        <v>460</v>
+        <v>49.08</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="I17">
-        <v>265.75204563977178</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>18.2</v>
+        <v>290</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>173.5</v>
+        <v>176.7804215788817</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G18">
-        <v>18.2</v>
+        <v>290</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="I18">
-        <v>180.93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>375</v>
+      </c>
+      <c r="D19">
+        <v>136.6</v>
+      </c>
+      <c r="E19">
+        <v>265.75</v>
+      </c>
+      <c r="F19">
+        <v>-0</v>
+      </c>
+      <c r="G19">
+        <v>375</v>
+      </c>
+      <c r="H19">
+        <v>110</v>
+      </c>
+      <c r="I19">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>460</v>
+      </c>
+      <c r="D20">
+        <v>158.72</v>
+      </c>
+      <c r="E20">
+        <v>323.8974215788817</v>
+      </c>
+      <c r="F20">
+        <v>58.14742157888168</v>
+      </c>
+      <c r="G20">
+        <v>460</v>
+      </c>
+      <c r="H20">
+        <v>110</v>
+      </c>
+      <c r="I20">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>460</v>
+      </c>
+      <c r="D21">
+        <v>174.96</v>
+      </c>
+      <c r="E21">
+        <v>296.9124215788817</v>
+      </c>
+      <c r="F21">
+        <v>31.16242157888168</v>
+      </c>
+      <c r="G21">
+        <v>460</v>
+      </c>
+      <c r="H21">
+        <v>110</v>
+      </c>
+      <c r="I21">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
         <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>33</v>
-      </c>
-      <c r="H19">
-        <v>20</v>
-      </c>
-      <c r="I19">
-        <v>180.93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>62</v>
-      </c>
-      <c r="H20">
-        <v>20</v>
-      </c>
-      <c r="I20">
-        <v>180.93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>90</v>
-      </c>
-      <c r="H21">
-        <v>20</v>
-      </c>
-      <c r="I21">
-        <v>180.93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>9</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22">
-        <v>27.61</v>
+        <v>18.2</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>177.59645230960589</v>
+        <v>173.5</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G22">
-        <v>27.61</v>
+        <v>18.2</v>
       </c>
       <c r="H22">
-        <v>20</v>
+        <v>3.4</v>
       </c>
       <c r="I22">
-        <v>353.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
+        <v>173.5</v>
+      </c>
+      <c r="F23">
+        <v>-0</v>
+      </c>
+      <c r="G23">
+        <v>33</v>
+      </c>
+      <c r="H23">
+        <v>3.4</v>
+      </c>
+      <c r="I23">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>62</v>
+      </c>
+      <c r="D24">
+        <v>5.4</v>
+      </c>
+      <c r="E24">
+        <v>262.4695784211183</v>
+      </c>
+      <c r="F24">
+        <v>81.53957842111831</v>
+      </c>
+      <c r="G24">
+        <v>62</v>
+      </c>
+      <c r="H24">
+        <v>3.4</v>
+      </c>
+      <c r="I24">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25">
+        <v>90</v>
+      </c>
+      <c r="D25">
+        <v>6.4</v>
+      </c>
+      <c r="E25">
+        <v>320.617</v>
+      </c>
+      <c r="F25">
+        <v>139.687</v>
+      </c>
+      <c r="G25">
+        <v>90</v>
+      </c>
+      <c r="H25">
+        <v>3.4</v>
+      </c>
+      <c r="I25">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>90</v>
+      </c>
+      <c r="D26">
+        <v>7.399999999999999</v>
+      </c>
+      <c r="E26">
+        <v>293.632</v>
+      </c>
+      <c r="F26">
+        <v>112.702</v>
+      </c>
+      <c r="G26">
+        <v>90</v>
+      </c>
+      <c r="H26">
+        <v>3.4</v>
+      </c>
+      <c r="I26">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>27.61</v>
+      </c>
+      <c r="D27">
         <v>0</v>
       </c>
-      <c r="F23">
+      <c r="E27">
+        <v>177.5964523096059</v>
+      </c>
+      <c r="F27">
+        <v>-0</v>
+      </c>
+      <c r="G27">
+        <v>27.61</v>
+      </c>
+      <c r="H27">
+        <v>293</v>
+      </c>
+      <c r="I27">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28">
+        <v>90.56</v>
+      </c>
+      <c r="D28">
         <v>0</v>
       </c>
-      <c r="G23">
+      <c r="E28">
+        <v>177.5964523096059</v>
+      </c>
+      <c r="F28">
+        <v>-0</v>
+      </c>
+      <c r="G28">
         <v>90.56</v>
       </c>
-      <c r="H23">
-        <v>20</v>
-      </c>
-      <c r="I23">
+      <c r="H28">
+        <v>293</v>
+      </c>
+      <c r="I28">
         <v>353.38</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
         <v>9</v>
       </c>
-      <c r="B24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24">
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>130</v>
+      </c>
+      <c r="D29">
         <v>0</v>
       </c>
-      <c r="D24">
+      <c r="E29">
+        <v>266.5660307307242</v>
+      </c>
+      <c r="F29">
+        <v>-0</v>
+      </c>
+      <c r="G29">
+        <v>130</v>
+      </c>
+      <c r="H29">
+        <v>293</v>
+      </c>
+      <c r="I29">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30">
+        <v>180</v>
+      </c>
+      <c r="D30">
         <v>0</v>
       </c>
-      <c r="E24">
+      <c r="E30">
+        <v>324.7134523096059</v>
+      </c>
+      <c r="F30">
+        <v>-0</v>
+      </c>
+      <c r="G30">
+        <v>180</v>
+      </c>
+      <c r="H30">
+        <v>293</v>
+      </c>
+      <c r="I30">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>180</v>
+      </c>
+      <c r="D31">
         <v>0</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>130</v>
-      </c>
-      <c r="H24">
-        <v>20</v>
-      </c>
-      <c r="I24">
-        <v>353.38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
+      <c r="E31">
+        <v>297.7284523096059</v>
+      </c>
+      <c r="F31">
+        <v>-0</v>
+      </c>
+      <c r="G31">
         <v>180</v>
       </c>
-      <c r="H25">
-        <v>20</v>
-      </c>
-      <c r="I25">
+      <c r="H31">
+        <v>293</v>
+      </c>
+      <c r="I31">
         <v>353.38</v>
       </c>
     </row>
